--- a/Configs/Localization/本地化.xlsx
+++ b/Configs/Localization/本地化.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12790" activeTab="1"/>
+    <workbookView windowWidth="27930" windowHeight="12975"/>
   </bookViews>
   <sheets>
     <sheet name="ChineseSimplified" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="36">
   <si>
     <t>##var</t>
   </si>
@@ -115,6 +115,24 @@
     <t>计时:</t>
   </si>
   <si>
+    <t>SettingForm.Setting</t>
+  </si>
+  <si>
+    <t>设置</t>
+  </si>
+  <si>
+    <t>SettingForm.Music</t>
+  </si>
+  <si>
+    <t>音乐</t>
+  </si>
+  <si>
+    <t>SettingForm.Effect</t>
+  </si>
+  <si>
+    <t>音效</t>
+  </si>
+  <si>
     <t>Monster Surviver</t>
   </si>
   <si>
@@ -128,6 +146,15 @@
   </si>
   <si>
     <t>Timer:</t>
+  </si>
+  <si>
+    <t>Setting</t>
+  </si>
+  <si>
+    <t>Music</t>
+  </si>
+  <si>
+    <t>Effect</t>
   </si>
 </sst>
 </file>
@@ -135,10 +162,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -646,19 +673,19 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1141,7 +1168,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:AJ16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.225" customWidth="1"/>
     <col min="2" max="2" width="6.75" customWidth="1"/>
@@ -1458,6 +1485,15 @@
       <c r="N10" s="4"/>
     </row>
     <row r="11" spans="1:36">
+      <c r="B11">
+        <v>6</v>
+      </c>
+      <c r="C11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" t="s">
+        <v>23</v>
+      </c>
       <c r="H11" s="3"/>
       <c r="J11" s="3"/>
       <c r="L11" s="3"/>
@@ -1465,7 +1501,15 @@
       <c r="N11" s="4"/>
     </row>
     <row r="12" spans="1:36">
-      <c r="C12" s="3"/>
+      <c r="B12">
+        <v>7</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12" t="s">
+        <v>25</v>
+      </c>
       <c r="H12" s="3"/>
       <c r="J12" s="3"/>
       <c r="L12" s="3"/>
@@ -1473,6 +1517,15 @@
       <c r="N12" s="4"/>
     </row>
     <row r="13" spans="1:36">
+      <c r="B13">
+        <v>8</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13" t="s">
+        <v>27</v>
+      </c>
       <c r="H13" s="3"/>
       <c r="J13" s="3"/>
       <c r="L13" s="3"/>
@@ -1523,8 +1576,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N10"/>
-  <sheetFormatPr defaultColWidth="15.1666666666667" defaultRowHeight="14"/>
+  <dimension ref="A1:N13"/>
+  <sheetFormatPr defaultColWidth="15.1666666666667" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="16384" width="15.1666666666667" customWidth="1"/>
   </cols>
@@ -1595,7 +1648,7 @@
         <v>12</v>
       </c>
       <c r="D6" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="H6" s="3"/>
       <c r="J6" s="3"/>
@@ -1611,7 +1664,7 @@
         <v>14</v>
       </c>
       <c r="D7" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="H7" s="3"/>
       <c r="J7" s="3"/>
@@ -1627,7 +1680,7 @@
         <v>16</v>
       </c>
       <c r="D8" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H8" s="3"/>
       <c r="J8" s="3"/>
@@ -1643,7 +1696,7 @@
         <v>18</v>
       </c>
       <c r="D9" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="H9" s="3"/>
       <c r="J9" s="3"/>
@@ -1659,7 +1712,7 @@
         <v>20</v>
       </c>
       <c r="D10" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="H10" s="3"/>
       <c r="J10" s="3"/>
@@ -1667,6 +1720,39 @@
       <c r="M10" s="4"/>
       <c r="N10" s="4"/>
     </row>
+    <row r="11" spans="1:14">
+      <c r="B11">
+        <v>6</v>
+      </c>
+      <c r="C11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="B12">
+        <v>7</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="B13">
+        <v>8</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13" t="s">
+        <v>35</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
